--- a/jay dashbord 2.xlsx
+++ b/jay dashbord 2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C20549A-7197-498D-BB5C-F3447C68B615}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAEBD653-E504-4466-BDE6-615A9687251F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{BCD9D06E-2ACE-420F-8923-CD1E9E7EFA4D}"/>
   </bookViews>
@@ -16416,12 +16416,12 @@
       <sheetName val="Sheet2"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
+      <sheetData sheetId="0" refreshError="1"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
       <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
